--- a/Accumulation_Scanner_2026-05-14.xlsx
+++ b/Accumulation_Scanner_2026-05-14.xlsx
@@ -8,11 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📅 Scan Info" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="💪 Strong Accum" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📈 Above EMA200" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📋 All Qualified" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🔍 Relaxed Prime" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🔍 Relaxed All" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📈 Above EMA200" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📋 All Qualified" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🔍 Relaxed Prime" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🔍 Relaxed All" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -54,7 +53,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -63,22 +62,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001B5E20"/>
+        <fgColor rgb="00006064"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F5E9"/>
+        <fgColor rgb="00E3F2FD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF9C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00006064"/>
       </patternFill>
     </fill>
     <fill>
@@ -93,12 +87,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0037474F"/>
+        <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E3F2FD"/>
+        <fgColor rgb="0037474F"/>
       </patternFill>
     </fill>
     <fill>
@@ -130,15 +124,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -168,23 +162,17 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -567,7 +555,7 @@
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>14-May-2026  00:50 IST</t>
+          <t>14-May-2026  20:19 IST</t>
         </is>
       </c>
     </row>
@@ -711,7 +699,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -831,7 +819,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -843,7 +831,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -862,12 +850,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -1029,12 +1017,12 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>BLSE</t>
+          <t>BUTTERFLY</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>💪 STRONG</t>
+          <t>✅ MODERATE</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
@@ -1043,37 +1031,37 @@
         </is>
       </c>
       <c r="E2" s="8" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>190.23</v>
+        <v>700.1</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>4.37</v>
+        <v>4.02</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>-37.24</v>
+        <v>-43.99</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>-18.18</v>
+        <v>-15.64</v>
       </c>
       <c r="K2" s="7" t="n">
         <v>3</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M2" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N2" s="7" t="n">
-        <v>2.5</v>
+        <v>48.7</v>
       </c>
       <c r="O2" s="7" t="n">
-        <v>29</v>
+        <v>27.7</v>
       </c>
       <c r="P2" s="7" t="inlineStr">
         <is>
@@ -1086,21 +1074,21 @@
         </is>
       </c>
       <c r="R2" s="7" t="n">
-        <v>14.51</v>
+        <v>12.28</v>
       </c>
       <c r="S2" s="7" t="n">
-        <v>-4.44</v>
+        <v>12.12</v>
       </c>
       <c r="T2" s="7" t="inlineStr">
         <is>
-          <t>9d ago</t>
+          <t>Today</t>
         </is>
       </c>
       <c r="U2" s="7" t="n">
-        <v>17.5</v>
+        <v>13.4</v>
       </c>
       <c r="V2" s="7" t="n">
-        <v>9.1</v>
+        <v>11.2</v>
       </c>
       <c r="W2" s="7" t="inlineStr">
         <is>
@@ -1113,14 +1101,14 @@
         </is>
       </c>
       <c r="Y2" s="7" t="n">
-        <v>176.21</v>
+        <v>626.91</v>
       </c>
       <c r="Z2" s="7" t="n">
-        <v>180.25</v>
+        <v>657.67</v>
       </c>
       <c r="AA2" s="7" t="inlineStr">
         <is>
-          <t>4.0L</t>
+          <t>36.1k</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1127,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -1306,12 +1294,12 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>BLSE</t>
+          <t>BUTTERFLY</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>💪 STRONG</t>
+          <t>✅ MODERATE</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
@@ -1320,37 +1308,37 @@
         </is>
       </c>
       <c r="E2" s="8" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>190.23</v>
+        <v>700.1</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>4.37</v>
+        <v>4.02</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>-37.24</v>
+        <v>-43.99</v>
       </c>
       <c r="J2" s="7" t="n">
-        <v>-18.18</v>
+        <v>-15.64</v>
       </c>
       <c r="K2" s="7" t="n">
         <v>3</v>
       </c>
       <c r="L2" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M2" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N2" s="7" t="n">
-        <v>2.5</v>
+        <v>48.7</v>
       </c>
       <c r="O2" s="7" t="n">
-        <v>29</v>
+        <v>27.7</v>
       </c>
       <c r="P2" s="7" t="inlineStr">
         <is>
@@ -1363,21 +1351,21 @@
         </is>
       </c>
       <c r="R2" s="7" t="n">
-        <v>14.51</v>
+        <v>12.28</v>
       </c>
       <c r="S2" s="7" t="n">
-        <v>-4.44</v>
+        <v>12.12</v>
       </c>
       <c r="T2" s="7" t="inlineStr">
         <is>
-          <t>9d ago</t>
+          <t>Today</t>
         </is>
       </c>
       <c r="U2" s="7" t="n">
-        <v>17.5</v>
+        <v>13.4</v>
       </c>
       <c r="V2" s="7" t="n">
-        <v>9.1</v>
+        <v>11.2</v>
       </c>
       <c r="W2" s="7" t="inlineStr">
         <is>
@@ -1390,14 +1378,14 @@
         </is>
       </c>
       <c r="Y2" s="7" t="n">
-        <v>176.21</v>
+        <v>626.91</v>
       </c>
       <c r="Z2" s="7" t="n">
-        <v>180.25</v>
+        <v>657.67</v>
       </c>
       <c r="AA2" s="7" t="inlineStr">
         <is>
-          <t>4.0L</t>
+          <t>36.1k</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1409,7 @@
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -1528,7 +1516,7 @@
       </c>
       <c r="R1" s="12" t="inlineStr">
         <is>
-          <t>Price Chg 20D %</t>
+          <t>Price Chg 30D %</t>
         </is>
       </c>
       <c r="S1" s="12" t="inlineStr">
@@ -1578,103 +1566,103 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="n">
+      <c r="A2" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>BLSE</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>DEEDEV</t>
+        </is>
+      </c>
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>💪 STRONG</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>📈 Accumulating</t>
         </is>
       </c>
       <c r="E2" s="8" t="n">
-        <v>65</v>
-      </c>
-      <c r="F2" s="7" t="n">
-        <v>70</v>
-      </c>
-      <c r="G2" s="7" t="n">
-        <v>190.23</v>
-      </c>
-      <c r="H2" s="7" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="I2" s="7" t="n">
-        <v>-37.24</v>
-      </c>
-      <c r="J2" s="7" t="n">
-        <v>-18.18</v>
-      </c>
-      <c r="K2" s="7" t="n">
+        <v>66</v>
+      </c>
+      <c r="F2" s="14" t="n">
+        <v>98</v>
+      </c>
+      <c r="G2" s="14" t="n">
+        <v>498.4</v>
+      </c>
+      <c r="H2" s="14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I2" s="14" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="J2" s="14" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="K2" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="L2" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="M2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N2" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O2" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="P2" s="7" t="inlineStr">
+      <c r="L2" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="M2" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="N2" s="14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O2" s="14" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="P2" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q2" s="7" t="inlineStr">
+      <c r="Q2" s="14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R2" s="7" t="n">
-        <v>14.51</v>
-      </c>
-      <c r="S2" s="7" t="n">
-        <v>-4.44</v>
-      </c>
-      <c r="T2" s="7" t="inlineStr">
-        <is>
-          <t>9d ago</t>
-        </is>
-      </c>
-      <c r="U2" s="7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="V2" s="7" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W2" s="7" t="inlineStr">
+      <c r="R2" s="14" t="n">
+        <v>72.34</v>
+      </c>
+      <c r="S2" s="14" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="T2" s="14" t="inlineStr">
+        <is>
+          <t>22d ago</t>
+        </is>
+      </c>
+      <c r="U2" s="14" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="V2" s="14" t="n">
+        <v>132.7</v>
+      </c>
+      <c r="W2" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="X2" s="7" t="inlineStr">
+      <c r="X2" s="14" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Y2" s="7" t="n">
-        <v>176.21</v>
-      </c>
-      <c r="Z2" s="7" t="n">
-        <v>180.25</v>
-      </c>
-      <c r="AA2" s="7" t="inlineStr">
-        <is>
-          <t>4.0L</t>
+      <c r="Y2" s="14" t="n">
+        <v>371.61</v>
+      </c>
+      <c r="Z2" s="14" t="n">
+        <v>292.03</v>
+      </c>
+      <c r="AA2" s="14" t="inlineStr">
+        <is>
+          <t>14.8L</t>
         </is>
       </c>
     </row>
@@ -1689,389 +1677,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA3"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
-    <col width="17" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="15" customWidth="1" min="24" max="24"/>
-    <col width="9" customWidth="1" min="25" max="25"/>
-    <col width="9" customWidth="1" min="26" max="26"/>
-    <col width="10" customWidth="1" min="27" max="27"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="13" t="n"/>
-      <c r="B1" s="14" t="inlineStr">
-        <is>
-          <t>Symbol</t>
-        </is>
-      </c>
-      <c r="C1" s="14" t="inlineStr">
-        <is>
-          <t>Grade</t>
-        </is>
-      </c>
-      <c r="D1" s="14" t="inlineStr">
-        <is>
-          <t>Setup Type</t>
-        </is>
-      </c>
-      <c r="E1" s="14" t="inlineStr">
-        <is>
-          <t>Accum Score</t>
-        </is>
-      </c>
-      <c r="F1" s="14" t="inlineStr">
-        <is>
-          <t>RS Rating</t>
-        </is>
-      </c>
-      <c r="G1" s="14" t="inlineStr">
-        <is>
-          <t>CMP</t>
-        </is>
-      </c>
-      <c r="H1" s="14" t="inlineStr">
-        <is>
-          <t>ADR %</t>
-        </is>
-      </c>
-      <c r="I1" s="14" t="inlineStr">
-        <is>
-          <t>% from ATH</t>
-        </is>
-      </c>
-      <c r="J1" s="14" t="inlineStr">
-        <is>
-          <t>% from 52W High</t>
-        </is>
-      </c>
-      <c r="K1" s="14" t="inlineStr">
-        <is>
-          <t>Up Days (Buy)</t>
-        </is>
-      </c>
-      <c r="L1" s="14" t="inlineStr">
-        <is>
-          <t>Down Days (Quiet)</t>
-        </is>
-      </c>
-      <c r="M1" s="14" t="inlineStr">
-        <is>
-          <t>Dist Days</t>
-        </is>
-      </c>
-      <c r="N1" s="14" t="inlineStr">
-        <is>
-          <t>U/D Vol Ratio</t>
-        </is>
-      </c>
-      <c r="O1" s="14" t="inlineStr">
-        <is>
-          <t>Base Depth %</t>
-        </is>
-      </c>
-      <c r="P1" s="14" t="inlineStr">
-        <is>
-          <t>Coiling</t>
-        </is>
-      </c>
-      <c r="Q1" s="14" t="inlineStr">
-        <is>
-          <t>Tight Base</t>
-        </is>
-      </c>
-      <c r="R1" s="14" t="inlineStr">
-        <is>
-          <t>Price Chg 30D %</t>
-        </is>
-      </c>
-      <c r="S1" s="14" t="inlineStr">
-        <is>
-          <t>Price Chg 5D %</t>
-        </is>
-      </c>
-      <c r="T1" s="14" t="inlineStr">
-        <is>
-          <t>Last Buy Signal</t>
-        </is>
-      </c>
-      <c r="U1" s="14" t="inlineStr">
-        <is>
-          <t>1M Return %</t>
-        </is>
-      </c>
-      <c r="V1" s="14" t="inlineStr">
-        <is>
-          <t>3M Return %</t>
-        </is>
-      </c>
-      <c r="W1" s="14" t="inlineStr">
-        <is>
-          <t>Above EMA50</t>
-        </is>
-      </c>
-      <c r="X1" s="14" t="inlineStr">
-        <is>
-          <t>Above EMA200</t>
-        </is>
-      </c>
-      <c r="Y1" s="14" t="inlineStr">
-        <is>
-          <t>EMA50</t>
-        </is>
-      </c>
-      <c r="Z1" s="14" t="inlineStr">
-        <is>
-          <t>EMA200</t>
-        </is>
-      </c>
-      <c r="AA1" s="14" t="inlineStr">
-        <is>
-          <t>Avg Vol</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>PRECWIRE</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>💪 STRONG</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>📈 Accumulating</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="n">
-        <v>69</v>
-      </c>
-      <c r="F2" s="7" t="n">
-        <v>98</v>
-      </c>
-      <c r="G2" s="7" t="n">
-        <v>389.05</v>
-      </c>
-      <c r="H2" s="7" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="I2" s="7" t="n">
-        <v>-12.67</v>
-      </c>
-      <c r="J2" s="7" t="n">
-        <v>-12.67</v>
-      </c>
-      <c r="K2" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="L2" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="M2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N2" s="7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="O2" s="7" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="P2" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q2" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R2" s="7" t="n">
-        <v>29.08</v>
-      </c>
-      <c r="S2" s="7" t="n">
-        <v>-1.38</v>
-      </c>
-      <c r="T2" s="7" t="inlineStr">
-        <is>
-          <t>16d ago</t>
-        </is>
-      </c>
-      <c r="U2" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="V2" s="7" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="W2" s="7" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="X2" s="7" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Y2" s="7" t="n">
-        <v>354.03</v>
-      </c>
-      <c r="Z2" s="7" t="n">
-        <v>270.19</v>
-      </c>
-      <c r="AA2" s="7" t="inlineStr">
-        <is>
-          <t>10.8L</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>DEEDEV</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>💪 STRONG</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>📈 Accumulating</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="n">
-        <v>66</v>
-      </c>
-      <c r="F3" s="7" t="n">
-        <v>98</v>
-      </c>
-      <c r="G3" s="7" t="n">
-        <v>490.45</v>
-      </c>
-      <c r="H3" s="7" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="I3" s="7" t="n">
-        <v>-4.02</v>
-      </c>
-      <c r="J3" s="7" t="n">
-        <v>-4.02</v>
-      </c>
-      <c r="K3" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="L3" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="M3" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="N3" s="7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O3" s="7" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="P3" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q3" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R3" s="7" t="n">
-        <v>76.01000000000001</v>
-      </c>
-      <c r="S3" s="7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="T3" s="7" t="inlineStr">
-        <is>
-          <t>20d ago</t>
-        </is>
-      </c>
-      <c r="U3" s="7" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="V3" s="7" t="n">
-        <v>134.6</v>
-      </c>
-      <c r="W3" s="7" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="X3" s="7" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Y3" s="7" t="n">
-        <v>361.2</v>
-      </c>
-      <c r="Z3" s="7" t="n">
-        <v>287.9</v>
-      </c>
-      <c r="AA3" s="7" t="inlineStr">
-        <is>
-          <t>14.8L</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AA6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -2094,7 +1704,7 @@
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
-    <col width="9" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
     <col width="9" customWidth="1" min="26" max="26"/>
     <col width="10" customWidth="1" min="27" max="27"/>
   </cols>
@@ -2233,507 +1843,1012 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="n">
+      <c r="A2" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>PRECWIRE</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>ONEPOINT</t>
+        </is>
+      </c>
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>💪 STRONG</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>🌀 Contracting</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="n">
+        <v>77</v>
+      </c>
+      <c r="F2" s="14" t="n">
+        <v>94</v>
+      </c>
+      <c r="G2" s="14" t="n">
+        <v>61.58</v>
+      </c>
+      <c r="H2" s="14" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="I2" s="14" t="n">
+        <v>-20.54</v>
+      </c>
+      <c r="J2" s="14" t="n">
+        <v>-12.02</v>
+      </c>
+      <c r="K2" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="L2" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="M2" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="N2" s="14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O2" s="14" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="P2" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q2" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R2" s="14" t="n">
+        <v>39.86</v>
+      </c>
+      <c r="S2" s="14" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="T2" s="14" t="inlineStr">
+        <is>
+          <t>Today</t>
+        </is>
+      </c>
+      <c r="U2" s="14" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="V2" s="14" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="W2" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X2" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y2" s="14" t="n">
+        <v>53.26</v>
+      </c>
+      <c r="Z2" s="14" t="n">
+        <v>51.54</v>
+      </c>
+      <c r="AA2" s="14" t="inlineStr">
+        <is>
+          <t>10.5L</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>BERGEPAINT</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>💪 STRONG</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>📈 Accumulating</t>
         </is>
       </c>
-      <c r="E2" s="8" t="n">
-        <v>69</v>
-      </c>
-      <c r="F2" s="7" t="n">
+      <c r="E3" s="8" t="n">
+        <v>74</v>
+      </c>
+      <c r="F3" s="14" t="n">
+        <v>56</v>
+      </c>
+      <c r="G3" s="14" t="n">
+        <v>533.9</v>
+      </c>
+      <c r="H3" s="14" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="I3" s="14" t="n">
+        <v>-15.19</v>
+      </c>
+      <c r="J3" s="14" t="n">
+        <v>-11.75</v>
+      </c>
+      <c r="K3" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L3" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="M3" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="14" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="O3" s="14" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="P3" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q3" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R3" s="14" t="n">
+        <v>27.79</v>
+      </c>
+      <c r="S3" s="14" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="T3" s="14" t="inlineStr">
+        <is>
+          <t>Today</t>
+        </is>
+      </c>
+      <c r="U3" s="14" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="V3" s="14" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="W3" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X3" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y3" s="14" t="n">
+        <v>469.09</v>
+      </c>
+      <c r="Z3" s="14" t="n">
+        <v>496.66</v>
+      </c>
+      <c r="AA3" s="14" t="inlineStr">
+        <is>
+          <t>3.6L</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>DEEDEV</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>💪 STRONG</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>📈 Accumulating</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>66</v>
+      </c>
+      <c r="F4" s="14" t="n">
         <v>98</v>
       </c>
-      <c r="G2" s="7" t="n">
-        <v>389.05</v>
-      </c>
-      <c r="H2" s="7" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="I2" s="7" t="n">
-        <v>-12.67</v>
-      </c>
-      <c r="J2" s="7" t="n">
-        <v>-12.67</v>
-      </c>
-      <c r="K2" s="7" t="n">
+      <c r="G4" s="14" t="n">
+        <v>498.4</v>
+      </c>
+      <c r="H4" s="14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I4" s="14" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="J4" s="14" t="n">
+        <v>-2.47</v>
+      </c>
+      <c r="K4" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="L2" s="7" t="n">
+      <c r="L4" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="M4" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" s="14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O4" s="14" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="P4" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q4" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R4" s="14" t="n">
+        <v>72.34</v>
+      </c>
+      <c r="S4" s="14" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="T4" s="14" t="inlineStr">
+        <is>
+          <t>22d ago</t>
+        </is>
+      </c>
+      <c r="U4" s="14" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="V4" s="14" t="n">
+        <v>132.7</v>
+      </c>
+      <c r="W4" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X4" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y4" s="14" t="n">
+        <v>371.61</v>
+      </c>
+      <c r="Z4" s="14" t="n">
+        <v>292.03</v>
+      </c>
+      <c r="AA4" s="14" t="inlineStr">
+        <is>
+          <t>14.8L</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>INDGN</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>💪 STRONG</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>📈 Accumulating</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>515.8</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>-29.95</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>-18.5</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L5" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="M5" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" s="14" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="P5" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q5" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R5" s="14" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="S5" s="14" t="n">
+        <v>-2.68</v>
+      </c>
+      <c r="T5" s="14" t="inlineStr">
+        <is>
+          <t>8d ago</t>
+        </is>
+      </c>
+      <c r="U5" s="14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="V5" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="W5" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X5" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y5" s="14" t="n">
+        <v>496.25</v>
+      </c>
+      <c r="Z5" s="14" t="n">
+        <v>515.24</v>
+      </c>
+      <c r="AA5" s="14" t="inlineStr">
+        <is>
+          <t>4.0L</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>PRAKASH</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>💪 STRONG</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>📈 Accumulating</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>63</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="G6" s="14" t="n">
+        <v>147.06</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="I6" s="14" t="n">
+        <v>-37.95</v>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>-22.96</v>
+      </c>
+      <c r="K6" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="M6" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" s="14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O6" s="14" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="P6" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q6" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R6" s="14" t="n">
+        <v>22.06</v>
+      </c>
+      <c r="S6" s="14" t="n">
+        <v>-3.38</v>
+      </c>
+      <c r="T6" s="14" t="inlineStr">
+        <is>
+          <t>9d ago</t>
+        </is>
+      </c>
+      <c r="U6" s="14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="V6" s="14" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="W6" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X6" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y6" s="14" t="n">
+        <v>138.02</v>
+      </c>
+      <c r="Z6" s="14" t="n">
+        <v>142.95</v>
+      </c>
+      <c r="AA6" s="14" t="inlineStr">
+        <is>
+          <t>4.7L</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>RICOAUTO</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>💪 STRONG</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>📈 Accumulating</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>68</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>115.06</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>-22.78</v>
+      </c>
+      <c r="J7" s="14" t="n">
+        <v>-19.2</v>
+      </c>
+      <c r="K7" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="M7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O7" s="14" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="P7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R7" s="14" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="S7" s="14" t="n">
+        <v>-9</v>
+      </c>
+      <c r="T7" s="14" t="inlineStr">
+        <is>
+          <t>5d ago</t>
+        </is>
+      </c>
+      <c r="U7" s="14" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="V7" s="14" t="n">
+        <v>-14.1</v>
+      </c>
+      <c r="W7" s="14" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="X7" s="14" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y7" s="14" t="n">
+        <v>116.1</v>
+      </c>
+      <c r="Z7" s="14" t="n">
+        <v>108.67</v>
+      </c>
+      <c r="AA7" s="14" t="inlineStr">
+        <is>
+          <t>22.9L</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>KRISHNADEF</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>✅ MODERATE</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>📈 Accumulating</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>57</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>97</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>1122.8</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>-14.49</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>-14.49</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" s="7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O8" s="7" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R8" s="7" t="n">
+        <v>27.01</v>
+      </c>
+      <c r="S8" s="7" t="n">
+        <v>-5.92</v>
+      </c>
+      <c r="T8" s="7" t="inlineStr">
+        <is>
+          <t>4d ago</t>
+        </is>
+      </c>
+      <c r="U8" s="7" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="V8" s="7" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="W8" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X8" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y8" s="7" t="n">
+        <v>1035.22</v>
+      </c>
+      <c r="Z8" s="7" t="n">
+        <v>912.76</v>
+      </c>
+      <c r="AA8" s="7" t="inlineStr">
+        <is>
+          <t>1.5L</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>GPTINFRA</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>✅ MODERATE</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>📈 Accumulating</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>115.72</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>-43.27</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>-22.75</v>
+      </c>
+      <c r="K9" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O9" s="7" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R9" s="7" t="n">
+        <v>19.58</v>
+      </c>
+      <c r="S9" s="7" t="n">
+        <v>-1.62</v>
+      </c>
+      <c r="T9" s="7" t="inlineStr">
+        <is>
+          <t>9d ago</t>
+        </is>
+      </c>
+      <c r="U9" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V9" s="7" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="W9" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X9" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y9" s="7" t="n">
+        <v>112.98</v>
+      </c>
+      <c r="Z9" s="7" t="n">
+        <v>113.97</v>
+      </c>
+      <c r="AA9" s="7" t="inlineStr">
+        <is>
+          <t>2.6L</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>EASEMYTRIP</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>✅ MODERATE</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>📈 Accumulating</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>54</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>-64.81</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>-33.95</v>
+      </c>
+      <c r="K10" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O10" s="7" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R10" s="7" t="n">
+        <v>28.82</v>
+      </c>
+      <c r="S10" s="7" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="T10" s="7" t="inlineStr">
+        <is>
+          <t>Today</t>
+        </is>
+      </c>
+      <c r="U10" s="7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="V10" s="7" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="W10" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="X10" s="7" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="Y10" s="7" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="Z10" s="7" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="AA10" s="7" t="inlineStr">
+        <is>
+          <t>1.8Cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="M2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N2" s="7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="O2" s="7" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="P2" s="7" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>IGIL</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>✅ MODERATE</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>📈 Accumulating</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>49</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>325.85</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>-49.27</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>-26.28</v>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" s="7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O11" s="7" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q2" s="7" t="inlineStr">
+      <c r="Q11" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R2" s="7" t="n">
-        <v>29.08</v>
-      </c>
-      <c r="S2" s="7" t="n">
-        <v>-1.38</v>
-      </c>
-      <c r="T2" s="7" t="inlineStr">
-        <is>
-          <t>16d ago</t>
-        </is>
-      </c>
-      <c r="U2" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="V2" s="7" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="W2" s="7" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="X2" s="7" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Y2" s="7" t="n">
-        <v>354.03</v>
-      </c>
-      <c r="Z2" s="7" t="n">
-        <v>270.19</v>
-      </c>
-      <c r="AA2" s="7" t="inlineStr">
-        <is>
-          <t>10.8L</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="n">
+      <c r="R11" s="7" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="S11" s="7" t="n">
+        <v>-8.02</v>
+      </c>
+      <c r="T11" s="7" t="inlineStr">
+        <is>
+          <t>20d ago</t>
+        </is>
+      </c>
+      <c r="U11" s="7" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="V11" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>DEEDEV</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>💪 STRONG</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>📈 Accumulating</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="n">
-        <v>66</v>
-      </c>
-      <c r="F3" s="7" t="n">
-        <v>98</v>
-      </c>
-      <c r="G3" s="7" t="n">
-        <v>490.45</v>
-      </c>
-      <c r="H3" s="7" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="I3" s="7" t="n">
-        <v>-4.02</v>
-      </c>
-      <c r="J3" s="7" t="n">
-        <v>-4.02</v>
-      </c>
-      <c r="K3" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="L3" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="M3" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="N3" s="7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O3" s="7" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="P3" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q3" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R3" s="7" t="n">
-        <v>76.01000000000001</v>
-      </c>
-      <c r="S3" s="7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="T3" s="7" t="inlineStr">
-        <is>
-          <t>20d ago</t>
-        </is>
-      </c>
-      <c r="U3" s="7" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="V3" s="7" t="n">
-        <v>134.6</v>
-      </c>
-      <c r="W3" s="7" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="X3" s="7" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Y3" s="7" t="n">
-        <v>361.2</v>
-      </c>
-      <c r="Z3" s="7" t="n">
-        <v>287.9</v>
-      </c>
-      <c r="AA3" s="7" t="inlineStr">
-        <is>
-          <t>14.8L</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="18" t="inlineStr">
-        <is>
-          <t>GPTINFRA</t>
-        </is>
-      </c>
-      <c r="C4" s="18" t="inlineStr">
-        <is>
-          <t>✅ MODERATE</t>
-        </is>
-      </c>
-      <c r="D4" s="18" t="inlineStr">
-        <is>
-          <t>🌀 Contracting</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="n">
-        <v>51</v>
-      </c>
-      <c r="F4" s="18" t="n">
-        <v>58</v>
-      </c>
-      <c r="G4" s="18" t="n">
-        <v>112.81</v>
-      </c>
-      <c r="H4" s="18" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="I4" s="18" t="n">
-        <v>-44.7</v>
-      </c>
-      <c r="J4" s="18" t="n">
-        <v>-24.69</v>
-      </c>
-      <c r="K4" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" s="18" t="n">
-        <v>14</v>
-      </c>
-      <c r="M4" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="N4" s="18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O4" s="18" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="P4" s="18" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q4" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R4" s="18" t="n">
-        <v>7.96</v>
-      </c>
-      <c r="S4" s="18" t="n">
-        <v>-4.97</v>
-      </c>
-      <c r="T4" s="18" t="inlineStr">
-        <is>
-          <t>7d ago</t>
-        </is>
-      </c>
-      <c r="U4" s="18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V4" s="18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="W4" s="18" t="inlineStr">
+      <c r="W11" s="7" t="inlineStr">
         <is>
           <t>✗</t>
         </is>
       </c>
-      <c r="X4" s="18" t="inlineStr">
+      <c r="X11" s="7" t="inlineStr">
         <is>
           <t>✗</t>
         </is>
       </c>
-      <c r="Y4" s="18" t="n">
-        <v>112.82</v>
-      </c>
-      <c r="Z4" s="18" t="n">
-        <v>113.95</v>
-      </c>
-      <c r="AA4" s="18" t="inlineStr">
-        <is>
-          <t>2.4L</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="18" t="inlineStr">
-        <is>
-          <t>IGIL</t>
-        </is>
-      </c>
-      <c r="C5" s="18" t="inlineStr">
-        <is>
-          <t>✅ MODERATE</t>
-        </is>
-      </c>
-      <c r="D5" s="18" t="inlineStr">
-        <is>
-          <t>📈 Accumulating</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>49</v>
-      </c>
-      <c r="F5" s="18" t="n">
-        <v>50</v>
-      </c>
-      <c r="G5" s="18" t="n">
-        <v>327.1</v>
-      </c>
-      <c r="H5" s="18" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="I5" s="18" t="n">
-        <v>-49.07</v>
-      </c>
-      <c r="J5" s="18" t="n">
-        <v>-26</v>
-      </c>
-      <c r="K5" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L5" s="18" t="n">
-        <v>13</v>
-      </c>
-      <c r="M5" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" s="18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="O5" s="18" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="P5" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q5" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R5" s="18" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="S5" s="18" t="n">
-        <v>-10.17</v>
-      </c>
-      <c r="T5" s="18" t="inlineStr">
-        <is>
-          <t>19d ago</t>
-        </is>
-      </c>
-      <c r="U5" s="18" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="V5" s="18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="W5" s="18" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="X5" s="18" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Y5" s="18" t="n">
-        <v>340.75</v>
-      </c>
-      <c r="Z5" s="18" t="n">
-        <v>346.94</v>
-      </c>
-      <c r="AA5" s="18" t="inlineStr">
-        <is>
-          <t>7.1L</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>PFOCUS</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>✅ MODERATE</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>📈 Accumulating</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="F6" s="18" t="n">
-        <v>98</v>
-      </c>
-      <c r="G6" s="18" t="n">
-        <v>288.8</v>
-      </c>
-      <c r="H6" s="18" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="I6" s="18" t="n">
-        <v>-21.31</v>
-      </c>
-      <c r="J6" s="18" t="n">
-        <v>-21.31</v>
-      </c>
-      <c r="K6" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" s="18" t="n">
-        <v>15</v>
-      </c>
-      <c r="M6" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" s="18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="O6" s="18" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="P6" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q6" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R6" s="18" t="n">
-        <v>-11.7</v>
-      </c>
-      <c r="S6" s="18" t="n">
-        <v>-3.77</v>
-      </c>
-      <c r="T6" s="18" t="inlineStr">
-        <is>
-          <t>26d ago</t>
-        </is>
-      </c>
-      <c r="U6" s="18" t="n">
-        <v>-14.4</v>
-      </c>
-      <c r="V6" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="W6" s="18" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="X6" s="18" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Y6" s="18" t="n">
-        <v>299.94</v>
-      </c>
-      <c r="Z6" s="18" t="n">
-        <v>234.29</v>
-      </c>
-      <c r="AA6" s="18" t="inlineStr">
-        <is>
-          <t>46.5L</t>
+      <c r="Y11" s="7" t="n">
+        <v>340.17</v>
+      </c>
+      <c r="Z11" s="7" t="n">
+        <v>346.73</v>
+      </c>
+      <c r="AA11" s="7" t="inlineStr">
+        <is>
+          <t>6.9L</t>
         </is>
       </c>
     </row>
